--- a/mca30.xlsx
+++ b/mca30.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ananye\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E414B7A-C3C6-408F-94DC-1CD2592846EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{6E414B7A-C3C6-408F-94DC-1CD2592846EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2395F8D1-9B2D-4790-9E9B-A4C9C9802D78}"/>
   <bookViews>
-    <workbookView xWindow="2184" yWindow="2436" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>A calm day</t>
+  </si>
+  <si>
+    <t>A soft yet powrful day</t>
   </si>
 </sst>
 </file>
@@ -2763,26 +2766,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B42" s="14">
+        <v>460</v>
+      </c>
+      <c r="C42" s="14">
+        <v>61</v>
+      </c>
+      <c r="D42" s="14">
+        <v>122</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>3</v>
+      </c>
+      <c r="H42" s="14">
+        <v>425</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1248</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>192</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/mca30.xlsx
+++ b/mca30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{6E414B7A-C3C6-408F-94DC-1CD2592846EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2395F8D1-9B2D-4790-9E9B-A4C9C9802D78}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{9C2CF09A-5F80-4A10-8875-D5129974D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   <si>
     <t>A soft yet powrful day</t>
   </si>
+  <si>
+    <t>a truly energetic day</t>
+  </si>
 </sst>
 </file>
 
@@ -611,6 +614,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2782,21 +2789,21 @@
         <v>30</v>
       </c>
       <c r="F42" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" s="14">
         <v>425</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1248</v>
+        <v>1098</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>192</v>
+        <v>342</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>57</v>
@@ -2812,26 +2819,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B43" s="14">
+        <v>540</v>
+      </c>
+      <c r="C43" s="14">
+        <v>66</v>
+      </c>
+      <c r="D43" s="14">
+        <v>101</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>123</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/mca30.xlsx
+++ b/mca30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{9C2CF09A-5F80-4A10-8875-D5129974D2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{2F63578F-A1DE-453A-9506-55E0E66AD15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,12 @@
   <si>
     <t>a truly energetic day</t>
   </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Couldn't sleep last night</t>
+  </si>
 </sst>
 </file>
 
@@ -614,10 +620,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2865,26 +2867,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B44" s="14">
+        <v>240</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14">
+        <v>25</v>
+      </c>
+      <c r="F44" s="14">
+        <v>150</v>
+      </c>
+      <c r="G44" s="14">
+        <v>3</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>815</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/mca30.xlsx
+++ b/mca30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{2F63578F-A1DE-453A-9506-55E0E66AD15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{B73E4C3D-35D2-49BC-AAA5-44EA1D835D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>Couldn't sleep last night</t>
+  </si>
+  <si>
+    <t>Again terrible sleep last night</t>
+  </si>
+  <si>
+    <t>A very average day</t>
   </si>
 </sst>
 </file>
@@ -2913,48 +2919,88 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
+      <c r="A45" s="13">
+        <v>46280</v>
+      </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="D45" s="14">
+        <v>30</v>
+      </c>
+      <c r="E45" s="14">
+        <v>123</v>
+      </c>
+      <c r="F45" s="14">
+        <v>300</v>
+      </c>
+      <c r="G45" s="14">
+        <v>8</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>573</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>867</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
+      <c r="A46" s="13">
+        <v>46281</v>
+      </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="D46" s="14">
+        <v>30</v>
+      </c>
+      <c r="E46" s="14">
+        <v>125</v>
+      </c>
+      <c r="F46" s="14">
+        <v>350</v>
+      </c>
+      <c r="G46" s="14">
+        <v>8</v>
+      </c>
+      <c r="H46" s="14">
+        <v>112</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>617</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>823</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/mca30.xlsx
+++ b/mca30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B73E4C3D-35D2-49BC-AAA5-44EA1D835D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{FBBBE986-F915-4F40-8DFA-82B258E67672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>A very average day</t>
+  </si>
+  <si>
+    <t>A swift day</t>
   </si>
 </sst>
 </file>
@@ -2922,8 +2925,12 @@
       <c r="A45" s="13">
         <v>46280</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>40</v>
+      </c>
       <c r="D45" s="14">
         <v>30</v>
       </c>
@@ -2941,11 +2948,11 @@
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>573</v>
+        <v>1093</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>867</v>
+        <v>347</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>59</v>
@@ -2964,8 +2971,12 @@
       <c r="A46" s="13">
         <v>46281</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>41</v>
+      </c>
       <c r="D46" s="14">
         <v>30</v>
       </c>
@@ -2983,11 +2994,11 @@
       </c>
       <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v>617</v>
+        <v>1138</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v>823</v>
+        <v>302</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>59</v>
@@ -3003,26 +3014,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>45</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>30</v>
+      </c>
+      <c r="F47" s="14">
+        <v>250</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
